--- a/data/flankseq/20251021-nonChr_markers_summary.xlsx
+++ b/data/flankseq/20251021-nonChr_markers_summary.xlsx
@@ -1,20 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dongyan.zhao/PycharmProjects/BI/grape_dartag_00_microhaplotype_db/data/flankseq/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36A54051-9C54-754B-A291-E3C54E2BC2FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05902251-75DD-AF4E-B550-E1637AB543F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2200" yWindow="660" windowWidth="28040" windowHeight="17440" xr2:uid="{915358BA-1CA2-5D46-BA02-5C515DB5798D}"/>
+    <workbookView xWindow="13420" yWindow="2100" windowWidth="28040" windowHeight="17440" xr2:uid="{915358BA-1CA2-5D46-BA02-5C515DB5798D}"/>
   </bookViews>
   <sheets>
-    <sheet name="20251021-nonChr_refAlt_lut" sheetId="3" r:id="rId1"/>
-    <sheet name="20251021-nonChr_refAlt_summary" sheetId="2" r:id="rId2"/>
+    <sheet name="20251021-nonChr_refAlt_summary" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="56">
   <si>
     <t>AGL11Exon7_000000071</t>
   </si>
@@ -202,40 +201,13 @@
   </si>
   <si>
     <t>GAAGCCCT</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>Lots of IUPAC throughout the amplicon</t>
-  </si>
-  <si>
-    <t>Note</t>
-  </si>
-  <si>
-    <t>Alt</t>
-  </si>
-  <si>
-    <t>Ref</t>
-  </si>
-  <si>
-    <t>Pos</t>
-  </si>
-  <si>
-    <t>AlleleID</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -368,13 +340,6 @@
       <color theme="0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -719,9 +684,8 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1096,965 +1060,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C21A4ED0-D3C2-F34E-B810-470020A28C53}">
-  <dimension ref="A1:I41"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="50.5" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F1" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>100</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2">
-        <v>100</v>
-      </c>
-      <c r="F2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3">
-        <v>84</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3">
-        <v>84</v>
-      </c>
-      <c r="F3" t="s">
-        <v>58</v>
-      </c>
-      <c r="G3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4">
-        <v>103</v>
-      </c>
-      <c r="C4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4">
-        <v>102</v>
-      </c>
-      <c r="F4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G4" t="s">
-        <v>54</v>
-      </c>
-      <c r="H4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5">
-        <v>60</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5">
-        <v>60</v>
-      </c>
-      <c r="F5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>53</v>
-      </c>
-      <c r="C6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>53</v>
-      </c>
-      <c r="F6" t="s">
-        <v>56</v>
-      </c>
-      <c r="G6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>94</v>
-      </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7">
-        <v>94</v>
-      </c>
-      <c r="F7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>61</v>
-      </c>
-      <c r="C8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8">
-        <v>61</v>
-      </c>
-      <c r="F8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9">
-        <v>34</v>
-      </c>
-      <c r="C9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9">
-        <v>34</v>
-      </c>
-      <c r="F9" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10">
-        <v>67</v>
-      </c>
-      <c r="C10" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10">
-        <v>67</v>
-      </c>
-      <c r="F10" t="s">
-        <v>54</v>
-      </c>
-      <c r="G10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11">
-        <v>109</v>
-      </c>
-      <c r="C11" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11">
-        <v>109</v>
-      </c>
-      <c r="F11" t="s">
-        <v>58</v>
-      </c>
-      <c r="G11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12">
-        <v>73</v>
-      </c>
-      <c r="C12" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12">
-        <v>73</v>
-      </c>
-      <c r="F12" t="s">
-        <v>56</v>
-      </c>
-      <c r="G12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13">
-        <v>87</v>
-      </c>
-      <c r="C13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13">
-        <v>87</v>
-      </c>
-      <c r="F13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G13" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14">
-        <v>70</v>
-      </c>
-      <c r="C14" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14">
-        <v>70</v>
-      </c>
-      <c r="F14" t="s">
-        <v>56</v>
-      </c>
-      <c r="G14" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15">
-        <v>99</v>
-      </c>
-      <c r="C15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15">
-        <v>99</v>
-      </c>
-      <c r="F15" t="s">
-        <v>58</v>
-      </c>
-      <c r="G15" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16">
-        <v>104</v>
-      </c>
-      <c r="C16" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16">
-        <v>104</v>
-      </c>
-      <c r="F16" t="s">
-        <v>58</v>
-      </c>
-      <c r="G16" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17">
-        <v>30</v>
-      </c>
-      <c r="C17" t="s">
-        <v>6</v>
-      </c>
-      <c r="D17" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17">
-        <v>30</v>
-      </c>
-      <c r="F17" t="s">
-        <v>54</v>
-      </c>
-      <c r="G17" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18">
-        <v>62</v>
-      </c>
-      <c r="C18" t="s">
-        <v>48</v>
-      </c>
-      <c r="D18" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18">
-        <v>62</v>
-      </c>
-      <c r="F18" t="s">
-        <v>54</v>
-      </c>
-      <c r="G18" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19">
-        <v>107</v>
-      </c>
-      <c r="C19" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" t="s">
-        <v>4</v>
-      </c>
-      <c r="E19">
-        <v>107</v>
-      </c>
-      <c r="F19" t="s">
-        <v>57</v>
-      </c>
-      <c r="G19" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20">
-        <v>46</v>
-      </c>
-      <c r="C20" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" t="s">
-        <v>4</v>
-      </c>
-      <c r="E20">
-        <v>46</v>
-      </c>
-      <c r="F20" t="s">
-        <v>56</v>
-      </c>
-      <c r="G20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21">
-        <v>44</v>
-      </c>
-      <c r="C21" t="s">
-        <v>6</v>
-      </c>
-      <c r="D21" t="s">
-        <v>4</v>
-      </c>
-      <c r="E21">
-        <v>44</v>
-      </c>
-      <c r="F21" t="s">
-        <v>58</v>
-      </c>
-      <c r="G21" t="s">
-        <v>56</v>
-      </c>
-      <c r="H21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22">
-        <v>34</v>
-      </c>
-      <c r="C22" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22">
-        <v>34</v>
-      </c>
-      <c r="F22" t="s">
-        <v>58</v>
-      </c>
-      <c r="G22" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23">
-        <v>94</v>
-      </c>
-      <c r="C23" t="s">
-        <v>6</v>
-      </c>
-      <c r="D23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23">
-        <v>94</v>
-      </c>
-      <c r="F23" t="s">
-        <v>54</v>
-      </c>
-      <c r="G23" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24">
-        <v>35</v>
-      </c>
-      <c r="C24" t="s">
-        <v>6</v>
-      </c>
-      <c r="D24" t="s">
-        <v>7</v>
-      </c>
-      <c r="E24">
-        <v>35</v>
-      </c>
-      <c r="F24" t="s">
-        <v>58</v>
-      </c>
-      <c r="G24" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>28</v>
-      </c>
-      <c r="B25">
-        <v>35</v>
-      </c>
-      <c r="C25" t="s">
-        <v>6</v>
-      </c>
-      <c r="D25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25">
-        <v>35</v>
-      </c>
-      <c r="F25" t="s">
-        <v>58</v>
-      </c>
-      <c r="G25" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26">
-        <v>34</v>
-      </c>
-      <c r="C26" t="s">
-        <v>6</v>
-      </c>
-      <c r="D26" t="s">
-        <v>7</v>
-      </c>
-      <c r="E26">
-        <v>34</v>
-      </c>
-      <c r="F26" t="s">
-        <v>57</v>
-      </c>
-      <c r="G26" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>30</v>
-      </c>
-      <c r="B27">
-        <v>81</v>
-      </c>
-      <c r="C27" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" t="s">
-        <v>4</v>
-      </c>
-      <c r="E27">
-        <v>81</v>
-      </c>
-      <c r="F27" t="s">
-        <v>56</v>
-      </c>
-      <c r="G27" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>31</v>
-      </c>
-      <c r="B28">
-        <v>97</v>
-      </c>
-      <c r="C28" t="s">
-        <v>6</v>
-      </c>
-      <c r="D28" t="s">
-        <v>7</v>
-      </c>
-      <c r="E28">
-        <v>97</v>
-      </c>
-      <c r="F28" t="s">
-        <v>58</v>
-      </c>
-      <c r="G28" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>32</v>
-      </c>
-      <c r="B29">
-        <v>28</v>
-      </c>
-      <c r="C29" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29" t="s">
-        <v>49</v>
-      </c>
-      <c r="E29">
-        <v>47</v>
-      </c>
-      <c r="F29" t="s">
-        <v>57</v>
-      </c>
-      <c r="G29" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>33</v>
-      </c>
-      <c r="B30">
-        <v>67</v>
-      </c>
-      <c r="C30" t="s">
-        <v>6</v>
-      </c>
-      <c r="D30" t="s">
-        <v>7</v>
-      </c>
-      <c r="E30">
-        <v>67</v>
-      </c>
-      <c r="F30" t="s">
-        <v>57</v>
-      </c>
-      <c r="G30" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>34</v>
-      </c>
-      <c r="B31">
-        <v>38</v>
-      </c>
-      <c r="C31" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" t="s">
-        <v>50</v>
-      </c>
-      <c r="E31">
-        <v>80</v>
-      </c>
-      <c r="F31" t="s">
-        <v>57</v>
-      </c>
-      <c r="G31" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>35</v>
-      </c>
-      <c r="B32">
-        <v>83</v>
-      </c>
-      <c r="C32" t="s">
-        <v>6</v>
-      </c>
-      <c r="D32" t="s">
-        <v>7</v>
-      </c>
-      <c r="E32">
-        <v>83</v>
-      </c>
-      <c r="F32" t="s">
-        <v>57</v>
-      </c>
-      <c r="G32" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>36</v>
-      </c>
-      <c r="B33">
-        <v>35</v>
-      </c>
-      <c r="C33" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" t="s">
-        <v>4</v>
-      </c>
-      <c r="E33">
-        <v>35</v>
-      </c>
-      <c r="F33" t="s">
-        <v>56</v>
-      </c>
-      <c r="G33" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34">
-        <v>30</v>
-      </c>
-      <c r="C34" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" t="s">
-        <v>4</v>
-      </c>
-      <c r="E34">
-        <v>30</v>
-      </c>
-      <c r="F34" t="s">
-        <v>56</v>
-      </c>
-      <c r="G34" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35">
-        <v>59</v>
-      </c>
-      <c r="C35" t="s">
-        <v>6</v>
-      </c>
-      <c r="D35" t="s">
-        <v>4</v>
-      </c>
-      <c r="E35">
-        <v>59</v>
-      </c>
-      <c r="F35" t="s">
-        <v>58</v>
-      </c>
-      <c r="G35" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36">
-        <v>36</v>
-      </c>
-      <c r="C36" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" t="s">
-        <v>4</v>
-      </c>
-      <c r="E36">
-        <v>36</v>
-      </c>
-      <c r="F36" t="s">
-        <v>56</v>
-      </c>
-      <c r="G36" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37">
-        <v>28</v>
-      </c>
-      <c r="C37" t="s">
-        <v>48</v>
-      </c>
-      <c r="D37" t="s">
-        <v>14</v>
-      </c>
-      <c r="E37">
-        <v>28</v>
-      </c>
-      <c r="F37" t="s">
-        <v>54</v>
-      </c>
-      <c r="G37" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38">
-        <v>85</v>
-      </c>
-      <c r="C38" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" t="s">
-        <v>4</v>
-      </c>
-      <c r="E38">
-        <v>85</v>
-      </c>
-      <c r="F38" t="s">
-        <v>57</v>
-      </c>
-      <c r="G38" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39">
-        <v>33</v>
-      </c>
-      <c r="C39" t="s">
-        <v>6</v>
-      </c>
-      <c r="D39" t="s">
-        <v>51</v>
-      </c>
-      <c r="E39">
-        <v>40</v>
-      </c>
-      <c r="F39" t="s">
-        <v>54</v>
-      </c>
-      <c r="G39" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40">
-        <v>75</v>
-      </c>
-      <c r="C40" t="s">
-        <v>6</v>
-      </c>
-      <c r="D40" t="s">
-        <v>49</v>
-      </c>
-      <c r="E40">
-        <v>105</v>
-      </c>
-      <c r="F40" t="s">
-        <v>56</v>
-      </c>
-      <c r="G40" t="s">
-        <v>54</v>
-      </c>
-      <c r="I40" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41">
-        <v>36</v>
-      </c>
-      <c r="C41" t="s">
-        <v>3</v>
-      </c>
-      <c r="D41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E41">
-        <v>36</v>
-      </c>
-      <c r="F41" t="s">
-        <v>56</v>
-      </c>
-      <c r="G41" t="s">
-        <v>54</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85DA988F-EB02-BB4D-9E64-2CCE3B8DD9A3}">
   <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
